--- a/html_sitemap_template.xlsx
+++ b/html_sitemap_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sumit Pandey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8545ABB3-7FE7-4F33-813A-5F1DADD4579A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083EF38A-513C-4127-9CE2-9B37DFCB126D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58A2AE8D-4FAE-493F-8E2B-D92984878DC7}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <r>
       <rPr>
@@ -80,9 +80,6 @@
     <t>Total Number of URLs</t>
   </si>
   <si>
-    <t>IN Existing</t>
-  </si>
-  <si>
     <t>URLs Not in HTML Sitemap</t>
   </si>
   <si>
@@ -110,288 +107,13 @@
     <t>Suggested Link</t>
   </si>
   <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/servers/</t>
-  </si>
-  <si>
-    <t>Servers</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Vanilla HTML</t>
-  </si>
-  <si>
-    <t>DATA CENTER PRODUCTS</t>
-  </si>
-  <si>
-    <t>DATA CENTER SOLUTIONS, SERVICES &amp; PARTNERS</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/storage/</t>
-  </si>
-  <si>
-    <t>storage</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/alliance/nvidia/</t>
-  </si>
-  <si>
-    <t>NVIDIA Solutions</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/sdi/</t>
-  </si>
-  <si>
-    <t>SOFTWARE-DEFINED INFRASTRUCTURE</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/services/</t>
-  </si>
-  <si>
-    <t>services</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/services/solution-services/</t>
-  </si>
-  <si>
-    <t>Solution Services</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/software/</t>
-  </si>
-  <si>
-    <t>SOFTWARE</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/software/cloud-marketplace/</t>
-  </si>
-  <si>
-    <t>Cloud Marketplace</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/software/infrastructure/</t>
-  </si>
-  <si>
-    <t>Infrastructure Software</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/software/lico/</t>
-  </si>
-  <si>
-    <t>Lenovo Intelligent Computing Orchestration (LiCO)</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/software/management/</t>
-  </si>
-  <si>
-    <t>Management Software</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/analytics-ai/</t>
-  </si>
-  <si>
-    <t>Analytics &amp; AI</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/big-data/</t>
-  </si>
-  <si>
-    <t>Big Data &amp; Analytics</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/business-applications/</t>
-  </si>
-  <si>
-    <t>Business Applications</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/cloud-computing/</t>
-  </si>
-  <si>
-    <t>Cloud Computing</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/cloud-service-provider/</t>
-  </si>
-  <si>
-    <t>Cloud Service Provider</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/database/</t>
-  </si>
-  <si>
-    <t>Database Solutions</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/devops/</t>
-  </si>
-  <si>
-    <t>DevOps</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/hpc/</t>
-  </si>
-  <si>
-    <t>High-Performance Computing (HPC)</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/microsoft/</t>
-  </si>
-  <si>
-    <t>Microsoft Solutions</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/oem/</t>
-  </si>
-  <si>
-    <t>OEM</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/redhat/</t>
-  </si>
-  <si>
-    <t>Red Hat Solutions</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/sap/</t>
-  </si>
-  <si>
-    <t>SAP Solutions</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/telco-nfv/</t>
-  </si>
-  <si>
-    <t>Telco Infrastructure Solutions</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/value-recovery/</t>
-  </si>
-  <si>
-    <t>Value Recovery</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/vmware/</t>
-  </si>
-  <si>
-    <t>VMware Solutions</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/sdi/thinkagile-mx-series/</t>
-  </si>
-  <si>
-    <t>ThinkAgile MX Series</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/p/servers-storage/networking/ethernet-switches/lenovo-thinksystem-ne2552e-flex-switch/77nwlem2552</t>
-  </si>
-  <si>
-    <t>ThinkSystem NE2552E Flex Switch</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/networking/</t>
-  </si>
-  <si>
-    <t>NETWORKING</t>
-  </si>
-  <si>
-    <r>
-      <t>Remove the link only</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> from anchor text as there is no dedicated Networking page.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/c/servers-storage/networking/ethernet-switches</t>
-  </si>
-  <si>
-    <t>Flex System Fabric EN4093R 10Gb Scalable Switch</t>
-  </si>
-  <si>
-    <t>Remove the anchor | Duplicate Link</t>
-  </si>
-  <si>
-    <t>Flex System Fabric SI4093 System Interconnect Module</t>
-  </si>
-  <si>
-    <t>Flex System SI4091 10Gb System Interconnect Module</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/c/servers-storage/servers/blades-flex</t>
-  </si>
-  <si>
-    <t>Blade Servers</t>
-  </si>
-  <si>
-    <t>Remove the anchor as we have no dedicated page for this</t>
-  </si>
-  <si>
-    <t>Flex System Blades</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/c/servers-storage/storage/storage-area-network</t>
-  </si>
-  <si>
-    <t>Storage Area Network System</t>
-  </si>
-  <si>
-    <t>Remove the anchor | Duplicate Anchor</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/c/servers-storage/storage/storage-tape</t>
-  </si>
-  <si>
-    <t>Tape Storage</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/c/servers-storage/storage/storage-area-network/san-fibre-channel-switches</t>
-  </si>
-  <si>
-    <t>ThinkSystem DB620S Storage</t>
-  </si>
-  <si>
-    <t>ThinkSystem DB630S Storage</t>
-  </si>
-  <si>
-    <t>ThinkSystem DB720S Storage</t>
-  </si>
-  <si>
-    <t>Cisco Nexus B22 Fabric Extender for Flex System</t>
-  </si>
-  <si>
-    <t>Flex System EN4091 10Gb Ethernet Pass-Thru Module</t>
-  </si>
-  <si>
-    <t>Flex System EN6131 40GB Ethernet Switch</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/networking</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/servers-storage/solutions/as-a-service/</t>
-  </si>
-  <si>
-    <t>As-a-Service</t>
-  </si>
-  <si>
-    <t>https://www.lenovo.com/in/en/c/servers-storage/storage/storage-area-network/ip-san-switches</t>
-  </si>
-  <si>
-    <t>BES-53248 Ethernet Storage Switch</t>
-  </si>
-  <si>
     <t>URLs Missing in HTML Sitemap</t>
   </si>
   <si>
     <t>Suggested Anchor Text</t>
+  </si>
+  <si>
+    <t>In Existing</t>
   </si>
 </sst>
 </file>
@@ -930,32 +652,19 @@
     </row>
     <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12">
-        <v>30</v>
-      </c>
-      <c r="C3" s="12">
-        <v>40</v>
-      </c>
-      <c r="D3" s="13">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="15">
-        <v>63</v>
-      </c>
-      <c r="C4" s="15">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16">
-        <f>B4+C4</f>
-        <v>63</v>
-      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -972,7 +681,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E4A82D-7346-4C79-9B83-A31FBE2A744B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H73"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -988,712 +696,338 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="18">
-        <v>200</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>18</v>
-      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
       <c r="G2" s="21"/>
       <c r="H2" s="17"/>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="18">
-        <v>200</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
       <c r="G3" s="21"/>
       <c r="H3" s="17"/>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="18">
-        <v>200</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="21"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="18">
-        <v>200</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="21"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="18">
-        <v>200</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="21"/>
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="18">
-        <v>200</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="21"/>
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="18">
-        <v>200</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="21"/>
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="18">
-        <v>200</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
       <c r="G9" s="21"/>
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="18">
-        <v>200</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
       <c r="G10" s="21"/>
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="18">
-        <v>200</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
       <c r="G11" s="21"/>
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="18">
-        <v>200</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
       <c r="G12" s="21"/>
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="18">
-        <v>200</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
       <c r="G13" s="21"/>
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="18">
-        <v>200</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
       <c r="G14" s="21"/>
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="18">
-        <v>200</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="21"/>
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="18">
-        <v>200</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
       <c r="G16" s="21"/>
       <c r="H16" s="17"/>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="18">
-        <v>200</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="21"/>
       <c r="H17" s="17"/>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="18">
-        <v>200</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
       <c r="G18" s="21"/>
       <c r="H18" s="17"/>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="18">
-        <v>200</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
       <c r="G19" s="21"/>
       <c r="H19" s="17"/>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="18">
-        <v>200</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
       <c r="G20" s="21"/>
       <c r="H20" s="17"/>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="18">
-        <v>200</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
       <c r="G21" s="21"/>
       <c r="H21" s="17"/>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="18">
-        <v>200</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
       <c r="G22" s="21"/>
       <c r="H22" s="17"/>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="18">
-        <v>200</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
       <c r="G23" s="21"/>
       <c r="H23" s="17"/>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="18">
-        <v>200</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
       <c r="G24" s="21"/>
       <c r="H24" s="17"/>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="18">
-        <v>200</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
       <c r="G25" s="21"/>
       <c r="H25" s="17"/>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="18">
-        <v>200</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
       <c r="G26" s="21"/>
       <c r="H26" s="17"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="18">
-        <v>200</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
       <c r="G27" s="21"/>
       <c r="H27" s="17"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="18">
-        <v>200</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
       <c r="G28" s="21"/>
       <c r="H28" s="17"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="18">
-        <v>200</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
       <c r="G29" s="21"/>
       <c r="H29" s="17"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="18">
-        <v>200</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
       <c r="G30" s="21"/>
       <c r="H30" s="17"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="18">
-        <v>200</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>18</v>
-      </c>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
       <c r="G31" s="21"/>
       <c r="H31" s="17"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="18">
-        <v>301</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>77</v>
-      </c>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="23"/>
       <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1746,124 +1080,54 @@
       <c r="G37" s="24"/>
       <c r="H37" s="17"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" s="18">
-        <v>302</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>80</v>
-      </c>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="24"/>
       <c r="H38" s="17"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="18">
-        <v>302</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39" s="24" t="s">
-        <v>80</v>
-      </c>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="24"/>
       <c r="H39" s="17"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="18">
-        <v>302</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" s="24" t="s">
-        <v>80</v>
-      </c>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="24"/>
       <c r="H40" s="17"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="18">
-        <v>302</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" s="24" t="s">
-        <v>85</v>
-      </c>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="24"/>
       <c r="H41" s="17"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="18">
-        <v>302</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G42" s="21" t="s">
-        <v>85</v>
-      </c>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="21"/>
       <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1876,52 +1140,24 @@
       <c r="G43" s="21"/>
       <c r="H43" s="17"/>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="18">
-        <v>302</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="21" t="s">
-        <v>89</v>
-      </c>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="21"/>
       <c r="H44" s="17"/>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="18">
-        <v>302</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>89</v>
-      </c>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="21"/>
       <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1964,148 +1200,64 @@
       <c r="G49" s="21"/>
       <c r="H49" s="17"/>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="18">
-        <v>302</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>85</v>
-      </c>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="21"/>
       <c r="H50" s="17"/>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" s="18">
-        <v>302</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>85</v>
-      </c>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="21"/>
       <c r="H51" s="17"/>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C52" s="18">
-        <v>302</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F52" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G52" s="21" t="s">
-        <v>85</v>
-      </c>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="21"/>
       <c r="H52" s="17"/>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C53" s="18">
-        <v>302</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" s="21" t="s">
-        <v>85</v>
-      </c>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="21"/>
       <c r="H53" s="17"/>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C54" s="18">
-        <v>302</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G54" s="21" t="s">
-        <v>85</v>
-      </c>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="21"/>
       <c r="H54" s="17"/>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" s="18">
-        <v>302</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G55" s="21" t="s">
-        <v>85</v>
-      </c>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="21"/>
       <c r="H55" s="17"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -2128,28 +1280,14 @@
       <c r="G57" s="21"/>
       <c r="H57" s="17"/>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="18">
-        <v>302</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" s="21" t="s">
-        <v>89</v>
-      </c>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="17"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="21"/>
       <c r="H58" s="17"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -2242,28 +1380,14 @@
       <c r="G67" s="24"/>
       <c r="H67" s="17"/>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B68" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C68" s="18">
-        <v>302</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="24" t="s">
-        <v>85</v>
-      </c>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="24"/>
       <c r="H68" s="17"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -2286,53 +1410,25 @@
       <c r="G70" s="24"/>
       <c r="H70" s="17"/>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C71" s="18">
-        <v>302</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G71" s="24" t="s">
-        <v>85</v>
-      </c>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="24"/>
       <c r="H71" s="17"/>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H73" xr:uid="{79E4A82D-7346-4C79-9B83-A31FBE2A744B}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="301"/>
-        <filter val="302"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Update the anchor text to &quot;Ethernet Switches for Flex&quot; also update the final link"/>
-        <filter val="Update the link"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2350,13 +1446,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2681,6 +1777,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b876f911-5672-4f93-94c1-ad5014161686">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="3fc1c0ae-3f08-4578-be13-2ba03192a863" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002644C4E5AAFF6B4295A8E23B6298BA64" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a55af01abb3b4b43035ce48c11a3e70d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="b876f911-5672-4f93-94c1-ad5014161686" xmlns:ns3="3fc1c0ae-3f08-4578-be13-2ba03192a863" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bfc42360d194a2e9131312274be4bb95" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2946,29 +2064,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B271BEA-00EC-45FA-9D47-2352F2164C04}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="b876f911-5672-4f93-94c1-ad5014161686"/>
+    <ds:schemaRef ds:uri="3fc1c0ae-3f08-4578-be13-2ba03192a863"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b876f911-5672-4f93-94c1-ad5014161686">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="3fc1c0ae-3f08-4578-be13-2ba03192a863" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65C217C4-510D-4B3E-8FA8-C3BB3DBDAB16}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FABD6AD-73DD-4979-8B82-F8E694B9F497}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2986,24 +2102,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65C217C4-510D-4B3E-8FA8-C3BB3DBDAB16}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B271BEA-00EC-45FA-9D47-2352F2164C04}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="b876f911-5672-4f93-94c1-ad5014161686"/>
-    <ds:schemaRef ds:uri="3fc1c0ae-3f08-4578-be13-2ba03192a863"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>